--- a/Lưu lượng Sản lượng Buôn Kuop 1977_2026.xlsx
+++ b/Lưu lượng Sản lượng Buôn Kuop 1977_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VScode\Du lieu truy van chuoi dong dang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8550753B-4491-4271-85A2-3AAF0DFEFBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2AF41B2-BEBE-4766-98F1-C86C2FC9C5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1575" windowWidth="29040" windowHeight="15960" xr2:uid="{8DBDBBA2-5905-4D19-AB7B-94BE22CB7CF3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{8DBDBBA2-5905-4D19-AB7B-94BE22CB7CF3}"/>
   </bookViews>
   <sheets>
     <sheet name="BK" sheetId="2" r:id="rId1"/>
@@ -1246,16 +1246,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C328C0-D6FB-438E-8F23-FDF170788131}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{10C328C0-D6FB-438E-8F23-FDF170788131}">
   <dimension ref="A1:AF71"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" ns3:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:32" ht="15" ns3:dyDescent="0.25">
       <c r="Q1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1271,7 +1271,7 @@
       <c r="AA1" s="23"/>
       <c r="AB1" s="23"/>
     </row>
-    <row r="2" spans="2:32" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:32" ht="15" ns3:dyDescent="0.25">
       <c r="C2" s="1">
         <v>1</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:32" ns3:dyDescent="0.2">
       <c r="B3">
         <v>1977</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:32" ns3:dyDescent="0.2">
       <c r="B4">
         <v>1978</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>167.2</v>
       </c>
     </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:32" ns3:dyDescent="0.2">
       <c r="B5">
         <v>1979</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>240.4</v>
       </c>
     </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:32" ns3:dyDescent="0.2">
       <c r="B6">
         <v>1980</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>240.1</v>
       </c>
     </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:32" ns3:dyDescent="0.2">
       <c r="B7">
         <v>1981</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>441.4</v>
       </c>
     </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:32" ns3:dyDescent="0.2">
       <c r="B8">
         <v>1982</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>94.4</v>
       </c>
     </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:32" ns3:dyDescent="0.2">
       <c r="B9">
         <v>1983</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>147.19999999999999</v>
       </c>
     </row>
-    <row r="10" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:32" ns3:dyDescent="0.2">
       <c r="B10">
         <v>1984</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>230.4</v>
       </c>
     </row>
-    <row r="11" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:32" ns3:dyDescent="0.2">
       <c r="B11">
         <v>1985</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>240.2</v>
       </c>
     </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:32" ns3:dyDescent="0.2">
       <c r="B12">
         <v>1986</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>313.10000000000002</v>
       </c>
     </row>
-    <row r="13" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:32" ns3:dyDescent="0.2">
       <c r="B13">
         <v>1987</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>196.1</v>
       </c>
     </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:32" ns3:dyDescent="0.2">
       <c r="B14">
         <v>1988</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:32" ns3:dyDescent="0.2">
       <c r="B15">
         <v>1989</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>139.5</v>
       </c>
     </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:32" ns3:dyDescent="0.2">
       <c r="B16">
         <v>1990</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:28" ns3:dyDescent="0.2">
       <c r="B17">
         <v>1991</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>96.7</v>
       </c>
     </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:28" ns3:dyDescent="0.2">
       <c r="B18">
         <v>1992</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>184.6</v>
       </c>
     </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:28" ns3:dyDescent="0.2">
       <c r="B19">
         <v>1993</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>590.4</v>
       </c>
     </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:28" ns3:dyDescent="0.2">
       <c r="B20">
         <v>1994</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>145.5</v>
       </c>
     </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:28" ns3:dyDescent="0.2">
       <c r="B21">
         <v>1995</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>222.3</v>
       </c>
     </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:28" ns3:dyDescent="0.2">
       <c r="B22">
         <v>1996</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:28" ns3:dyDescent="0.2">
       <c r="B23">
         <v>1997</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>115.5</v>
       </c>
     </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:28" ns3:dyDescent="0.2">
       <c r="B24">
         <v>1998</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>867.5</v>
       </c>
     </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:28" ns3:dyDescent="0.2">
       <c r="B25">
         <v>1999</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>662.8</v>
       </c>
     </row>
-    <row r="26" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:28" ns3:dyDescent="0.2">
       <c r="B26">
         <v>2000</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>551.5</v>
       </c>
     </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:28" ns3:dyDescent="0.2">
       <c r="B27">
         <v>2001</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:28" ns3:dyDescent="0.2">
       <c r="B28">
         <v>2002</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>180.5</v>
       </c>
     </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:28" ns3:dyDescent="0.2">
       <c r="B29">
         <v>2003</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>161.71377325659216</v>
       </c>
     </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:28" ns3:dyDescent="0.2">
       <c r="B30">
         <v>2004</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>78.943581849819296</v>
       </c>
     </row>
-    <row r="31" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:28" ns3:dyDescent="0.2">
       <c r="B31">
         <v>2005</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>661.06596718383753</v>
       </c>
     </row>
-    <row r="32" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:28" ns3:dyDescent="0.2">
       <c r="B32">
         <v>2006</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>141.33263284700843</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" ns3:dyDescent="0.2">
       <c r="B33">
         <v>2007</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>322.4689064382278</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:28" ns3:dyDescent="0.2">
       <c r="B34">
         <v>2008</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>422.01270244947131</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" ns3:dyDescent="0.2">
       <c r="B35">
         <v>2009</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" ns3:dyDescent="0.2">
       <c r="A36" s="7"/>
       <c r="B36" s="8">
         <v>2010</v>
@@ -4529,7 +4529,7 @@
         <v>311.84394761264713</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" ht="15" ns3:dyDescent="0.25">
       <c r="B37" s="1">
         <v>2011</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>217.26831637224768</v>
       </c>
     </row>
-    <row r="38" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" ht="15" ns3:dyDescent="0.25">
       <c r="B38" s="1">
         <v>2012</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>100.21832853302611</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="15" ns3:dyDescent="0.25">
       <c r="B39" s="1">
         <v>2013</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>141.83356086789553</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" ht="15" ns3:dyDescent="0.25">
       <c r="B40" s="1">
         <v>2014</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>98.869481886840703</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" ht="15" ns3:dyDescent="0.25">
       <c r="B41" s="1">
         <v>2015</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>76.222091973886634</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="15" ns3:dyDescent="0.25">
       <c r="B42" s="1">
         <v>2016</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>439.25057870370404</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="15" ns3:dyDescent="0.25">
       <c r="B43" s="1">
         <v>2017</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>417.73705879842902</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" ht="15" ns3:dyDescent="0.25">
       <c r="B44" s="1">
         <v>2018</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>177.05547427035367</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" ht="15" ns3:dyDescent="0.25">
       <c r="B45" s="1">
         <v>2019</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>130.82224249018637</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" ht="15" ns3:dyDescent="0.25">
       <c r="B46" s="1">
         <v>2020</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>478.93006666666662</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="15" ns3:dyDescent="0.25">
       <c r="B47" s="1">
         <v>2021</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>429.99193548387098</v>
       </c>
     </row>
-    <row r="48" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" ht="15" ns3:dyDescent="0.25">
       <c r="B48" s="1">
         <v>2022</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>234.77126807868515</v>
       </c>
     </row>
-    <row r="49" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B49" s="1">
         <v>2023</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>195.77149354838716</v>
       </c>
     </row>
-    <row r="50" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B50" s="1">
         <v>2024</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>220.07123870967743</v>
       </c>
     </row>
-    <row r="51" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B51" s="12">
         <v>2025</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>436.70027419354835</v>
       </c>
     </row>
-    <row r="52" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B52" s="1">
         <v>2026</v>
       </c>
@@ -5944,7 +5944,9 @@
       <c r="K52" s="6">
         <v>159.874</v>
       </c>
-      <c r="L52" s="6"/>
+      <c r="L52" s="6" t="n">
+        <v>83.5827994</v>
+      </c>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
       <c r="O52" s="11"/>
@@ -5976,8 +5978,11 @@
       <c r="Y52" s="6">
         <v>272.60000000000002</v>
       </c>
-    </row>
-    <row r="53" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+      <c r="Z52" s="6" t="n">
+        <v>332.23</v>
+      </c>
+    </row>
+    <row r="53" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B53" s="12"/>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
@@ -5994,7 +5999,7 @@
       <c r="O53" s="11"/>
       <c r="P53" s="3"/>
     </row>
-    <row r="54" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B54" s="12"/>
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
@@ -6011,7 +6016,7 @@
       <c r="O54" s="11"/>
       <c r="P54" s="3"/>
     </row>
-    <row r="55" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B55" s="24"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
@@ -6028,7 +6033,7 @@
       <c r="O55" s="14"/>
       <c r="P55" s="3"/>
     </row>
-    <row r="56" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B56" s="24"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
@@ -6044,7 +6049,7 @@
       <c r="N56" s="6"/>
       <c r="O56" s="14"/>
     </row>
-    <row r="58" spans="2:28" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:28" ht="15" ns3:dyDescent="0.25">
       <c r="B58" s="25"/>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
@@ -6061,7 +6066,7 @@
       <c r="O58" s="6"/>
       <c r="P58" s="3"/>
     </row>
-    <row r="59" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:28" ns3:dyDescent="0.2">
       <c r="B59" s="25"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
@@ -6077,7 +6082,7 @@
       <c r="N59" s="6"/>
       <c r="O59" s="6"/>
     </row>
-    <row r="60" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:28" ns3:dyDescent="0.2">
       <c r="C60" s="15"/>
       <c r="D60" s="15"/>
       <c r="E60" s="15"/>
@@ -6093,30 +6098,30 @@
       <c r="O60" s="15"/>
       <c r="P60" s="3"/>
     </row>
-    <row r="61" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:28" ns3:dyDescent="0.2">
       <c r="O61" s="16"/>
     </row>
-    <row r="62" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:28" ns3:dyDescent="0.2">
       <c r="O62" s="16"/>
     </row>
-    <row r="63" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:28" ns3:dyDescent="0.2">
       <c r="O63" s="17"/>
     </row>
-    <row r="68" spans="14:16" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="14:16" ht="15.75" ns3:dyDescent="0.2">
       <c r="N68" s="18"/>
       <c r="O68" s="18"/>
     </row>
-    <row r="69" spans="14:16" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="14:16" ht="15.75" ns3:dyDescent="0.2">
       <c r="N69" s="19"/>
       <c r="O69" s="18"/>
       <c r="P69" s="17"/>
     </row>
-    <row r="70" spans="14:16" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="14:16" ht="15.75" ns3:dyDescent="0.2">
       <c r="N70" s="20"/>
       <c r="O70" s="18"/>
       <c r="P70" s="17"/>
     </row>
-    <row r="71" spans="14:16" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="14:16" ht="15.75" ns3:dyDescent="0.2">
       <c r="N71" s="21"/>
       <c r="O71" s="18"/>
       <c r="P71" s="17"/>
